--- a/OH.xlsx
+++ b/OH.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -40,19 +40,22 @@
     <t xml:space="preserve">Intensity</t>
   </si>
   <si>
+    <t xml:space="preserve">Transition</t>
+  </si>
+  <si>
     <t xml:space="preserve">G003</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5</t>
+    <t xml:space="preserve">95.9</t>
   </si>
   <si>
     <t xml:space="preserve">25.0</t>
   </si>
   <si>
     <t xml:space="preserve">1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J=z-a</t>
   </si>
   <si>
     <t xml:space="preserve">G006</t>
@@ -82,6 +85,7 @@
       <sz val="10"/>
       <name val="DejaVu Sans"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -102,6 +106,7 @@
       <sz val="10"/>
       <name val="DejaVu Serif"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -146,16 +151,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -282,10 +291,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultColWidth="10.08203125" defaultRowHeight="13.15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -304,54 +313,63 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="2" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="n">
-        <v>800</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="C2" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>7940</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="G2" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="3" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+    <row r="3" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>1300</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
